--- a/data/trans_orig/LAWTONB_2R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R3-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40285</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64813</t>
+          <t>66920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96134</t>
+          <t>97205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136009</t>
+          <t>136238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146607</t>
+          <t>143509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192291</t>
+          <t>191124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308376</t>
+          <t>306269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>332269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>451740</t>
+          <t>451511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>491615</t>
+          <t>490544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>768647</t>
+          <t>769814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814331</t>
+          <t>817429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>70803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82962</t>
+          <t>82706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46728</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>123217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140047</t>
+          <t>139458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51284</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164711</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216682</t>
+          <t>215710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422082</t>
+          <t>421166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451182</t>
+          <t>449662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>529131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571200</t>
+          <t>571019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>962626</t>
+          <t>963598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014597</t>
+          <t>1014316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>79028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117544</t>
+          <t>114918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156241</t>
+          <t>155885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>201524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246412</t>
+          <t>245258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306126</t>
+          <t>304518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296854</t>
+          <t>299480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334758</t>
+          <t>335370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431023</t>
+          <t>433021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>478304</t>
+          <t>478660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742816</t>
+          <t>744424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>802530</t>
+          <t>803684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,82 +2694,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9648</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4405</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17536</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>26530</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>17150</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>38852</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9648</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16456</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>26530</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>18321</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>38033</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91194</t>
+          <t>92430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>109375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,82 +2807,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>92,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>73426</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>65538</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78669</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>78,89%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>175209</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>162887</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>184589</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>91,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>73426</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>66618</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78916</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>175209</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>163706</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>183418</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137651</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169489</t>
+          <t>168604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217566</t>
+          <t>215774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275388</t>
+          <t>271187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342098</t>
+          <t>338358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>421986</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462199</t>
+          <t>464284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522299</t>
+          <t>524091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570376</t>
+          <t>571261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>957404</t>
+          <t>961144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1024114</t>
+          <t>1028315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>56953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85903</t>
+          <t>85038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130838</t>
+          <t>131056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>176246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196272</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250671</t>
+          <t>248773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267998</t>
+          <t>268863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296813</t>
+          <t>296948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377038</t>
+          <t>378511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423919</t>
+          <t>423701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>657987</t>
+          <t>659885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712386</t>
+          <t>714383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56975</t>
+          <t>57105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170092</t>
+          <t>169763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184271</t>
+          <t>184196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146771</t>
+          <t>147303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169628</t>
+          <t>169649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323631</t>
+          <t>323501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349998</t>
+          <t>349997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72689</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73015</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105247</t>
+          <t>105186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>158675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209556</t>
+          <t>210016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242822</t>
+          <t>241938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305192</t>
+          <t>301381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483216</t>
+          <t>483277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515448</t>
+          <t>515179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566949</t>
+          <t>566489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>618104</t>
+          <t>617830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1059776</t>
+          <t>1063587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1122146</t>
+          <t>1123030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>74475</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60986</t>
+          <t>63171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84153</t>
+          <t>86112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>191111</t>
+          <t>205842</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176347</t>
+          <t>189822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>205425</t>
+          <t>223299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>262310</t>
+          <t>280317</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244102</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284583</t>
+          <t>301835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>194630</t>
+          <t>211867</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181676</t>
+          <t>200230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204843</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306778</t>
+          <t>329754</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292464</t>
+          <t>312297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>321542</t>
+          <t>345774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>501408</t>
+          <t>541621</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479135</t>
+          <t>520103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519616</t>
+          <t>562210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36245</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67613</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>70998</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92676</t>
+          <t>83139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>272258</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236392</t>
+          <t>262266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252417</t>
+          <t>279717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>419337</t>
+          <t>235606</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386404</t>
+          <t>226431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441627</t>
+          <t>243078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>663280</t>
+          <t>507865</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633978</t>
+          <t>495724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>700075</t>
+          <t>519746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97085</t>
+          <t>109541</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91717</t>
+          <t>103812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100509</t>
+          <t>113241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64383</t>
+          <t>74777</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60231</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67443</t>
+          <t>78089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>184319</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155645</t>
+          <t>176324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166053</t>
+          <t>189406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>106055</t>
+          <t>112951</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90887</t>
+          <t>97878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122401</t>
+          <t>129684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>232733</t>
+          <t>254018</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125137</t>
+          <t>233002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297673</t>
+          <t>273041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>338788</t>
+          <t>366969</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200321</t>
+          <t>342669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392729</t>
+          <t>395085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>535657</t>
+          <t>593666</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519311</t>
+          <t>576933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>550825</t>
+          <t>608739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>790498</t>
+          <t>640138</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>725558</t>
+          <t>621115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898094</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1326155</t>
+          <t>1233804</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1272214</t>
+          <t>1205688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1464622</t>
+          <t>1258104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
